--- a/コスト表.xlsx
+++ b/コスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yongy\git\2026_SpringGame\SpringGame_2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OsakiTowa\Desktop\2026_SpringGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33CD2797-95CA-441E-B795-E95BA8F2ECE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5F1D59A-2766-4601-A1CA-6C9AC1E35170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
+    <workbookView xWindow="4590" yWindow="1485" windowWidth="23760" windowHeight="13530" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="65">
   <si>
     <t>アニメーション</t>
     <phoneticPr fontId="2"/>
@@ -392,6 +392,13 @@
     <t>完全提出</t>
     <rPh sb="0" eb="4">
       <t>カンゼンテイシュツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>作業中</t>
+    <rPh sb="0" eb="3">
+      <t>サギョウチュウ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -784,7 +791,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -867,13 +874,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1514,11 +1514,11 @@
       </c>
       <c r="K8" s="2">
         <f>COUNTIF(H3:H35,J8)</f>
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="L8" s="2">
         <f>COUNTIF(H3:H35,J8)</f>
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.4">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="K9" s="12">
         <f>COUNTIF(H3:H35,J9)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L9" s="12"/>
     </row>
@@ -1591,8 +1591,8 @@
         <v>53</v>
       </c>
       <c r="K11" s="5">
-        <f ca="1">DATE(2026,4,13)-TODAY()</f>
-        <v>27</v>
+        <f ca="1">DATE(2026,4,17)-TODAY()</f>
+        <v>30</v>
       </c>
       <c r="M11" s="5"/>
     </row>
@@ -1615,12 +1615,12 @@
         <v>39</v>
       </c>
       <c r="I12" s="28"/>
-      <c r="J12" s="70" t="s">
+      <c r="J12" s="67" t="s">
         <v>52</v>
       </c>
       <c r="K12" s="5">
         <f ca="1">K4/K11</f>
-        <v>0.87037037037037035</v>
+        <v>0.78333333333333333</v>
       </c>
       <c r="L12" s="9"/>
       <c r="M12" s="9"/>
@@ -1689,15 +1689,13 @@
         <v>39</v>
       </c>
       <c r="I15" s="28"/>
-      <c r="J15" s="47" t="s">
+      <c r="J15" s="44" t="s">
         <v>54</v>
       </c>
-      <c r="K15" s="34"/>
-      <c r="L15" s="34"/>
-      <c r="M15" s="35"/>
-      <c r="N15" s="35"/>
-      <c r="O15" s="36"/>
-      <c r="P15" s="35"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="10"/>
+      <c r="P15" s="5"/>
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B16" s="7" t="s">
@@ -1720,25 +1718,25 @@
         <v>39</v>
       </c>
       <c r="I16" s="28"/>
-      <c r="J16" s="37" t="s">
+      <c r="J16" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="K16" s="38" t="s">
+      <c r="K16" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="L16" s="38" t="s">
+      <c r="L16" s="35" t="s">
         <v>57</v>
       </c>
-      <c r="M16" s="38" t="s">
+      <c r="M16" s="35" t="s">
         <v>58</v>
       </c>
-      <c r="N16" s="38" t="s">
+      <c r="N16" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="O16" s="39" t="s">
+      <c r="O16" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="P16" s="40" t="s">
+      <c r="P16" s="37" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1761,7 +1759,7 @@
         <v>39</v>
       </c>
       <c r="I17" s="29"/>
-      <c r="J17" s="41">
+      <c r="J17" s="38">
         <v>1</v>
       </c>
       <c r="K17" s="12">
@@ -1779,7 +1777,7 @@
       <c r="O17" s="12">
         <v>6</v>
       </c>
-      <c r="P17" s="42">
+      <c r="P17" s="39">
         <v>7</v>
       </c>
     </row>
@@ -1796,7 +1794,7 @@
         <v>39</v>
       </c>
       <c r="I18" s="5"/>
-      <c r="J18" s="41">
+      <c r="J18" s="38">
         <v>8</v>
       </c>
       <c r="K18" s="12">
@@ -1814,7 +1812,7 @@
       <c r="O18" s="12">
         <v>13</v>
       </c>
-      <c r="P18" s="42">
+      <c r="P18" s="39">
         <v>14</v>
       </c>
     </row>
@@ -1837,25 +1835,25 @@
         <v>39</v>
       </c>
       <c r="I19" s="5"/>
-      <c r="J19" s="43">
+      <c r="J19" s="40">
         <v>15</v>
       </c>
       <c r="K19" s="12">
         <v>16</v>
       </c>
-      <c r="L19" s="52">
+      <c r="L19" s="49">
         <v>17</v>
       </c>
-      <c r="M19" s="52">
+      <c r="M19" s="49">
         <v>18</v>
       </c>
-      <c r="N19" s="52">
+      <c r="N19" s="49">
         <v>19</v>
       </c>
-      <c r="O19" s="53">
+      <c r="O19" s="50">
         <v>20</v>
       </c>
-      <c r="P19" s="54">
+      <c r="P19" s="51">
         <v>21</v>
       </c>
     </row>
@@ -1878,25 +1876,25 @@
         <v>39</v>
       </c>
       <c r="I20" s="5"/>
-      <c r="J20" s="55">
+      <c r="J20" s="52">
         <v>22</v>
       </c>
-      <c r="K20" s="52">
+      <c r="K20" s="49">
         <v>23</v>
       </c>
-      <c r="L20" s="52">
+      <c r="L20" s="49">
         <v>24</v>
       </c>
-      <c r="M20" s="52">
+      <c r="M20" s="49">
         <v>25</v>
       </c>
-      <c r="N20" s="52">
+      <c r="N20" s="49">
         <v>26</v>
       </c>
-      <c r="O20" s="53">
+      <c r="O20" s="50">
         <v>27</v>
       </c>
-      <c r="P20" s="54">
+      <c r="P20" s="51">
         <v>28</v>
       </c>
     </row>
@@ -1913,19 +1911,19 @@
         <v>39</v>
       </c>
       <c r="I21" s="5"/>
-      <c r="J21" s="56">
+      <c r="J21" s="53">
         <v>29</v>
       </c>
-      <c r="K21" s="57">
+      <c r="K21" s="54">
         <v>30</v>
       </c>
-      <c r="L21" s="57">
+      <c r="L21" s="54">
         <v>31</v>
       </c>
-      <c r="M21" s="44"/>
-      <c r="N21" s="44"/>
-      <c r="O21" s="45"/>
-      <c r="P21" s="46"/>
+      <c r="M21" s="41"/>
+      <c r="N21" s="41"/>
+      <c r="O21" s="42"/>
+      <c r="P21" s="43"/>
     </row>
     <row r="22" spans="2:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B22" s="6"/>
@@ -1966,7 +1964,7 @@
       <c r="H23" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="J23" s="48" t="s">
+      <c r="J23" s="45" t="s">
         <v>62</v>
       </c>
       <c r="Q23" s="5"/>
@@ -1984,19 +1982,19 @@
       <c r="H24" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="J24" s="49"/>
-      <c r="K24" s="51"/>
-      <c r="L24" s="51"/>
-      <c r="M24" s="58">
+      <c r="J24" s="46"/>
+      <c r="K24" s="48"/>
+      <c r="L24" s="48"/>
+      <c r="M24" s="55">
         <v>1</v>
       </c>
-      <c r="N24" s="58">
+      <c r="N24" s="55">
         <v>2</v>
       </c>
-      <c r="O24" s="58">
+      <c r="O24" s="55">
         <v>3</v>
       </c>
-      <c r="P24" s="59">
+      <c r="P24" s="56">
         <v>4</v>
       </c>
       <c r="Q24" s="5"/>
@@ -2020,25 +2018,25 @@
       <c r="H25" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="J25" s="60">
+      <c r="J25" s="57">
         <v>5</v>
       </c>
-      <c r="K25" s="61">
+      <c r="K25" s="58">
         <v>6</v>
       </c>
-      <c r="L25" s="62">
+      <c r="L25" s="59">
         <v>7</v>
       </c>
-      <c r="M25" s="63">
+      <c r="M25" s="60">
         <v>8</v>
       </c>
-      <c r="N25" s="63">
+      <c r="N25" s="60">
         <v>9</v>
       </c>
-      <c r="O25" s="63">
+      <c r="O25" s="60">
         <v>10</v>
       </c>
-      <c r="P25" s="64">
+      <c r="P25" s="61">
         <v>11</v>
       </c>
       <c r="Q25" s="5"/>
@@ -2062,10 +2060,10 @@
       <c r="H26" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="J26" s="41">
+      <c r="J26" s="38">
         <v>12</v>
       </c>
-      <c r="K26" s="65">
+      <c r="K26" s="62">
         <v>13</v>
       </c>
       <c r="L26" s="12">
@@ -2080,7 +2078,7 @@
       <c r="O26" s="12">
         <v>17</v>
       </c>
-      <c r="P26" s="42">
+      <c r="P26" s="39">
         <v>18</v>
       </c>
       <c r="Q26" s="5"/>
@@ -2098,7 +2096,7 @@
       <c r="H27" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="J27" s="41">
+      <c r="J27" s="38">
         <v>19</v>
       </c>
       <c r="K27" s="33">
@@ -2116,7 +2114,7 @@
       <c r="O27" s="12">
         <v>24</v>
       </c>
-      <c r="P27" s="42">
+      <c r="P27" s="39">
         <v>25</v>
       </c>
     </row>
@@ -2134,27 +2132,29 @@
       <c r="F28" s="2">
         <v>2</v>
       </c>
-      <c r="G28" s="2"/>
+      <c r="G28" s="2">
+        <v>2</v>
+      </c>
       <c r="H28" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="J28" s="50">
+        <v>64</v>
+      </c>
+      <c r="J28" s="47">
         <v>26</v>
       </c>
-      <c r="K28" s="45">
+      <c r="K28" s="42">
         <v>27</v>
       </c>
-      <c r="L28" s="44">
+      <c r="L28" s="41">
         <v>28</v>
       </c>
-      <c r="M28" s="44">
+      <c r="M28" s="41">
         <v>29</v>
       </c>
-      <c r="N28" s="44">
+      <c r="N28" s="41">
         <v>30</v>
       </c>
-      <c r="O28" s="44"/>
-      <c r="P28" s="46"/>
+      <c r="O28" s="41"/>
+      <c r="P28" s="43"/>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.4">
       <c r="B29" s="6"/>
@@ -2170,9 +2170,11 @@
       <c r="F29" s="2">
         <v>2</v>
       </c>
-      <c r="G29" s="2"/>
+      <c r="G29" s="2">
+        <v>2</v>
+      </c>
       <c r="H29" s="18" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="M29" s="5"/>
       <c r="N29" s="5"/>
@@ -2191,9 +2193,11 @@
       <c r="F30" s="2">
         <v>2</v>
       </c>
-      <c r="G30" s="2"/>
+      <c r="G30" s="2">
+        <v>2</v>
+      </c>
       <c r="H30" s="18" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="M30" s="9"/>
       <c r="N30" s="9"/>
@@ -2210,7 +2214,7 @@
       <c r="H31" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="J31" s="66" t="s">
+      <c r="J31" s="63" t="s">
         <v>35</v>
       </c>
       <c r="M31" s="9"/>
@@ -2234,7 +2238,7 @@
       <c r="H32" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="J32" s="67" t="s">
+      <c r="J32" s="64" t="s">
         <v>36</v>
       </c>
       <c r="M32" s="5"/>
@@ -2258,7 +2262,7 @@
       <c r="H33" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="J33" s="68" t="s">
+      <c r="J33" s="65" t="s">
         <v>38</v>
       </c>
       <c r="M33" s="5"/>
@@ -2282,7 +2286,7 @@
       <c r="H34" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="J34" s="69" t="s">
+      <c r="J34" s="66" t="s">
         <v>63</v>
       </c>
       <c r="M34" s="5"/>

--- a/コスト表.xlsx
+++ b/コスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OsakiTowa\Desktop\2026_SpringGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5F1D59A-2766-4601-A1CA-6C9AC1E35170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11BD28AD-12C8-4523-8AE4-47551FBA7731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4590" yWindow="1485" windowWidth="23760" windowHeight="13530" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
+    <workbookView xWindow="2115" yWindow="975" windowWidth="24510" windowHeight="13530" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="66">
   <si>
     <t>アニメーション</t>
     <phoneticPr fontId="2"/>
@@ -399,6 +399,16 @@
     <t>作業中</t>
     <rPh sb="0" eb="3">
       <t>サギョウチュウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>全体の作業時間</t>
+    <rPh sb="0" eb="2">
+      <t>ゼンタイ</t>
+    </rPh>
+    <rPh sb="3" eb="7">
+      <t>サギョウジカン</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -450,7 +460,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -529,6 +539,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="18">
     <border>
@@ -791,7 +807,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -961,6 +977,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1404,10 +1426,10 @@
         <v>49</v>
       </c>
       <c r="K4" s="2">
-        <f>SUM(F3:F35)</f>
-        <v>23.5</v>
-      </c>
-      <c r="L4" s="2"/>
+        <f>COUNTA(H3:H35)</f>
+        <v>32</v>
+      </c>
+      <c r="L4" s="68"/>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B5" s="7"/>
@@ -1435,8 +1457,8 @@
         <v>12.5</v>
       </c>
       <c r="L5" s="2">
-        <f>SUMIF(E3:E35,"プロト",F3:F35)</f>
-        <v>12.5</v>
+        <f>SUMIFS(F:F, E:E, "プロト", H:H, "未完了")</f>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.4">
@@ -1465,7 +1487,7 @@
         <v>10</v>
       </c>
       <c r="L6" s="2">
-        <f>SUMIF(E3:E35,"アルファ",F3:F35)</f>
+        <f>SUMIFS(F:F, E:E, "アルファ", H:H, "未完了")</f>
         <v>10</v>
       </c>
     </row>
@@ -1487,7 +1509,7 @@
         <v>1</v>
       </c>
       <c r="L7" s="2">
-        <f>SUMIF(E3:E35,"ベータ",F3:F35)</f>
+        <f>SUMIFS(F:F, E:E, "ベータ", H:H, "未完了")</f>
         <v>1</v>
       </c>
     </row>
@@ -1517,7 +1539,7 @@
         <v>28</v>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIF(H3:H35,J8)</f>
+        <f>COUNTIF(H:H, "未完了")</f>
         <v>28</v>
       </c>
     </row>
@@ -1546,7 +1568,7 @@
         <f>COUNTIF(H3:H35,J9)</f>
         <v>3</v>
       </c>
-      <c r="L9" s="12"/>
+      <c r="L9" s="69"/>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B10" s="7" t="s">
@@ -1588,11 +1610,11 @@
       </c>
       <c r="I11" s="5"/>
       <c r="J11" t="s">
-        <v>53</v>
-      </c>
-      <c r="K11" s="5">
-        <f ca="1">DATE(2026,4,17)-TODAY()</f>
-        <v>30</v>
+        <v>65</v>
+      </c>
+      <c r="K11">
+        <f>SUM(F3:F35)</f>
+        <v>23.5</v>
       </c>
       <c r="M11" s="5"/>
     </row>
@@ -1615,12 +1637,12 @@
         <v>39</v>
       </c>
       <c r="I12" s="28"/>
-      <c r="J12" s="67" t="s">
-        <v>52</v>
+      <c r="J12" t="s">
+        <v>53</v>
       </c>
       <c r="K12" s="5">
-        <f ca="1">K4/K11</f>
-        <v>0.78333333333333333</v>
+        <f ca="1">DATE(2026,4,17)-TODAY()</f>
+        <v>30</v>
       </c>
       <c r="L12" s="9"/>
       <c r="M12" s="9"/>
@@ -1644,6 +1666,13 @@
         <v>39</v>
       </c>
       <c r="I13" s="28"/>
+      <c r="J13" s="67" t="s">
+        <v>52</v>
+      </c>
+      <c r="K13" s="5">
+        <f ca="1">K11/K12</f>
+        <v>0.78333333333333333</v>
+      </c>
       <c r="L13" s="5"/>
       <c r="M13" s="5"/>
     </row>

--- a/コスト表.xlsx
+++ b/コスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OsakiTowa\Desktop\2026_SpringGame\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yongy\git\2026_SpringGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11BD28AD-12C8-4523-8AE4-47551FBA7731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C93B0F3-F3F8-4F9F-84A2-62BE228ECF61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2115" yWindow="975" windowWidth="24510" windowHeight="13530" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
+    <workbookView minimized="1" xWindow="0" yWindow="1110" windowWidth="28485" windowHeight="14370" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="65">
   <si>
     <t>アニメーション</t>
     <phoneticPr fontId="2"/>
@@ -392,13 +392,6 @@
     <t>完全提出</t>
     <rPh sb="0" eb="4">
       <t>カンゼンテイシュツ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>作業中</t>
-    <rPh sb="0" eb="3">
-      <t>サギョウチュウ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -1566,7 +1559,7 @@
       </c>
       <c r="K9" s="12">
         <f>COUNTIF(H3:H35,J9)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L9" s="69"/>
     </row>
@@ -1610,7 +1603,7 @@
       </c>
       <c r="I11" s="5"/>
       <c r="J11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K11">
         <f>SUM(F3:F35)</f>
@@ -2165,7 +2158,7 @@
         <v>2</v>
       </c>
       <c r="H28" s="18" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="J28" s="47">
         <v>26</v>

--- a/コスト表.xlsx
+++ b/コスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yongy\git\2026_SpringGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C93B0F3-F3F8-4F9F-84A2-62BE228ECF61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42AB3F93-BC41-4F97-A423-B2ECE21702E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="1110" windowWidth="28485" windowHeight="14370" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
+    <workbookView xWindow="315" yWindow="60" windowWidth="28485" windowHeight="14370" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -952,9 +952,6 @@
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
@@ -975,6 +972,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1422,7 +1422,7 @@
         <f>COUNTA(H3:H35)</f>
         <v>32</v>
       </c>
-      <c r="L4" s="68"/>
+      <c r="L4" s="67"/>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B5" s="7"/>
@@ -1433,7 +1433,7 @@
         <v>31</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F5" s="2">
         <v>0.5</v>
@@ -1447,11 +1447,11 @@
       </c>
       <c r="K5" s="2">
         <f>SUMIF(E3:E35,"プロト",F3:F35)</f>
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="L5" s="2">
         <f>SUMIFS(F:F, E:E, "プロト", H:H, "未完了")</f>
-        <v>6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.4">
@@ -1463,7 +1463,7 @@
         <v>32</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F6" s="8">
         <v>1</v>
@@ -1477,11 +1477,11 @@
       </c>
       <c r="K6" s="2">
         <f>SUMIF(E3:E35,"アルファ",F3:F35)</f>
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="L6" s="2">
         <f>SUMIFS(F:F, E:E, "アルファ", H:H, "未完了")</f>
-        <v>10</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.4">
@@ -1529,11 +1529,11 @@
       </c>
       <c r="K8" s="2">
         <f>COUNTIF(H3:H35,J8)</f>
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L8" s="2">
         <f>COUNTIF(H:H, "未完了")</f>
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.4">
@@ -1559,9 +1559,9 @@
       </c>
       <c r="K9" s="12">
         <f>COUNTIF(H3:H35,J9)</f>
-        <v>4</v>
-      </c>
-      <c r="L9" s="69"/>
+        <v>6</v>
+      </c>
+      <c r="L9" s="68"/>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B10" s="7" t="s">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="K12" s="5">
         <f ca="1">DATE(2026,4,17)-TODAY()</f>
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="L12" s="9"/>
       <c r="M12" s="9"/>
@@ -1659,12 +1659,12 @@
         <v>39</v>
       </c>
       <c r="I13" s="28"/>
-      <c r="J13" s="67" t="s">
+      <c r="J13" s="66" t="s">
         <v>52</v>
       </c>
       <c r="K13" s="5">
         <f ca="1">K11/K12</f>
-        <v>0.78333333333333333</v>
+        <v>0.87037037037037035</v>
       </c>
       <c r="L13" s="5"/>
       <c r="M13" s="5"/>
@@ -2036,9 +2036,11 @@
       <c r="F25" s="8">
         <v>1</v>
       </c>
-      <c r="G25" s="2"/>
+      <c r="G25" s="2">
+        <v>0.5</v>
+      </c>
       <c r="H25" s="18" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="J25" s="57">
         <v>5</v>
@@ -2058,7 +2060,7 @@
       <c r="O25" s="60">
         <v>10</v>
       </c>
-      <c r="P25" s="61">
+      <c r="P25" s="69">
         <v>11</v>
       </c>
       <c r="Q25" s="5"/>
@@ -2078,14 +2080,16 @@
       <c r="F26" s="8">
         <v>1</v>
       </c>
-      <c r="G26" s="2"/>
+      <c r="G26" s="2">
+        <v>0.5</v>
+      </c>
       <c r="H26" s="18" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="J26" s="38">
         <v>12</v>
       </c>
-      <c r="K26" s="62">
+      <c r="K26" s="61">
         <v>13</v>
       </c>
       <c r="L26" s="12">
@@ -2236,7 +2240,7 @@
       <c r="H31" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="J31" s="63" t="s">
+      <c r="J31" s="62" t="s">
         <v>35</v>
       </c>
       <c r="M31" s="9"/>
@@ -2260,7 +2264,7 @@
       <c r="H32" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="J32" s="64" t="s">
+      <c r="J32" s="63" t="s">
         <v>36</v>
       </c>
       <c r="M32" s="5"/>
@@ -2284,7 +2288,7 @@
       <c r="H33" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="J33" s="65" t="s">
+      <c r="J33" s="64" t="s">
         <v>38</v>
       </c>
       <c r="M33" s="5"/>
@@ -2308,7 +2312,7 @@
       <c r="H34" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="J34" s="66" t="s">
+      <c r="J34" s="65" t="s">
         <v>63</v>
       </c>
       <c r="M34" s="5"/>

--- a/コスト表.xlsx
+++ b/コスト表.xlsx
@@ -5,29 +5,20 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yongy\git\2026_SpringGame\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Towa\2026_SpringGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42AB3F93-BC41-4F97-A423-B2ECE21702E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D950500-3C07-4655-B446-118201118A6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="315" yWindow="60" windowWidth="28485" windowHeight="14370" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -800,7 +791,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -972,9 +963,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1312,25 +1300,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{039B1606-320D-4390-8B98-CE6030BB2FAA}">
   <dimension ref="B1:R63"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="2" max="2" width="25.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="25.5" bestFit="1" customWidth="1"/>
     <col min="4" max="6" width="11.25" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.25" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.625" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.58203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="11.58203125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11" customWidth="1"/>
-    <col min="14" max="14" width="16.875" customWidth="1"/>
-    <col min="15" max="15" width="9.875" customWidth="1"/>
-    <col min="16" max="16" width="12.375" customWidth="1"/>
+    <col min="14" max="14" width="16.83203125" customWidth="1"/>
+    <col min="15" max="15" width="9.83203125" customWidth="1"/>
+    <col min="16" max="16" width="12.33203125" customWidth="1"/>
     <col min="17" max="17" width="9.25" customWidth="1"/>
-    <col min="18" max="18" width="9.625" customWidth="1"/>
+    <col min="18" max="18" width="9.58203125" customWidth="1"/>
     <col min="19" max="19" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:16" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B1" t="s">
         <v>30</v>
       </c>
@@ -1338,7 +1326,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B2" s="13" t="s">
         <v>21</v>
       </c>
@@ -1365,7 +1353,7 @@
       <c r="L2" s="9"/>
       <c r="M2" s="9"/>
     </row>
-    <row r="3" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="7" t="s">
         <v>2</v>
       </c>
@@ -1397,7 +1385,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="7"/>
       <c r="C4" s="3" t="s">
         <v>6</v>
@@ -1411,9 +1399,11 @@
       <c r="F4" s="2">
         <v>0.5</v>
       </c>
-      <c r="G4" s="4"/>
+      <c r="G4" s="4">
+        <v>0.5</v>
+      </c>
       <c r="H4" s="18" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>49</v>
@@ -1424,7 +1414,7 @@
       </c>
       <c r="L4" s="67"/>
     </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="7"/>
       <c r="C5" s="3" t="s">
         <v>7</v>
@@ -1451,10 +1441,10 @@
       </c>
       <c r="L5" s="2">
         <f>SUMIFS(F:F, E:E, "プロト", H:H, "未完了")</f>
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="7"/>
       <c r="C6" s="3" t="s">
         <v>51</v>
@@ -1484,7 +1474,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="7" t="s">
         <v>8</v>
       </c>
@@ -1506,7 +1496,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" s="7"/>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -1529,14 +1519,14 @@
       </c>
       <c r="K8" s="2">
         <f>COUNTIF(H3:H35,J8)</f>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L8" s="2">
         <f>COUNTIF(H:H, "未完了")</f>
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.4">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="7"/>
       <c r="C9" s="3" t="s">
         <v>7</v>
@@ -1559,11 +1549,11 @@
       </c>
       <c r="K9" s="12">
         <f>COUNTIF(H3:H35,J9)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L9" s="68"/>
     </row>
-    <row r="10" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" s="7" t="s">
         <v>0</v>
       </c>
@@ -1581,7 +1571,7 @@
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
     </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" s="7" t="s">
         <v>9</v>
       </c>
@@ -1611,7 +1601,7 @@
       </c>
       <c r="M11" s="5"/>
     </row>
-    <row r="12" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" s="7"/>
       <c r="C12" s="3" t="s">
         <v>6</v>
@@ -1635,12 +1625,12 @@
       </c>
       <c r="K12" s="5">
         <f ca="1">DATE(2026,4,17)-TODAY()</f>
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="L12" s="9"/>
       <c r="M12" s="9"/>
     </row>
-    <row r="13" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B13" s="7"/>
       <c r="C13" s="3" t="s">
         <v>1</v>
@@ -1664,12 +1654,12 @@
       </c>
       <c r="K13" s="5">
         <f ca="1">K11/K12</f>
-        <v>0.87037037037037035</v>
+        <v>0.94</v>
       </c>
       <c r="L13" s="5"/>
       <c r="M13" s="5"/>
     </row>
-    <row r="14" spans="2:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:16" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B14" s="7"/>
       <c r="C14" s="3" t="s">
         <v>7</v>
@@ -1692,7 +1682,7 @@
       <c r="K14" s="5"/>
       <c r="L14" s="5"/>
     </row>
-    <row r="15" spans="2:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:16" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B15" s="7"/>
       <c r="C15" s="3" t="s">
         <v>16</v>
@@ -1719,7 +1709,7 @@
       <c r="O15" s="10"/>
       <c r="P15" s="5"/>
     </row>
-    <row r="16" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" s="7" t="s">
         <v>11</v>
       </c>
@@ -1762,7 +1752,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:18" x14ac:dyDescent="0.55000000000000004">
       <c r="B17" s="6"/>
       <c r="C17" s="3" t="s">
         <v>7</v>
@@ -1803,7 +1793,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:18" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" s="6" t="s">
         <v>18</v>
       </c>
@@ -1838,7 +1828,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:18" x14ac:dyDescent="0.55000000000000004">
       <c r="B19" s="6"/>
       <c r="C19" s="3" t="s">
         <v>3</v>
@@ -1879,7 +1869,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:18" x14ac:dyDescent="0.55000000000000004">
       <c r="B20" s="6"/>
       <c r="C20" s="3" t="s">
         <v>4</v>
@@ -1920,7 +1910,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="2:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:18" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B21" s="6" t="s">
         <v>5</v>
       </c>
@@ -1947,7 +1937,7 @@
       <c r="O21" s="42"/>
       <c r="P21" s="43"/>
     </row>
-    <row r="22" spans="2:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:18" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B22" s="6"/>
       <c r="C22" s="3" t="s">
         <v>12</v>
@@ -1968,7 +1958,7 @@
       <c r="J22" s="5"/>
       <c r="K22" s="5"/>
     </row>
-    <row r="23" spans="2:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:18" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B23" s="6"/>
       <c r="C23" s="3" t="s">
         <v>13</v>
@@ -1992,7 +1982,7 @@
       <c r="Q23" s="5"/>
       <c r="R23" s="5"/>
     </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:18" x14ac:dyDescent="0.55000000000000004">
       <c r="B24" s="6" t="s">
         <v>17</v>
       </c>
@@ -2022,7 +2012,7 @@
       <c r="Q24" s="5"/>
       <c r="R24" s="5"/>
     </row>
-    <row r="25" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:18" x14ac:dyDescent="0.55000000000000004">
       <c r="B25" s="6"/>
       <c r="C25" s="3" t="s">
         <v>15</v>
@@ -2060,13 +2050,13 @@
       <c r="O25" s="60">
         <v>10</v>
       </c>
-      <c r="P25" s="69">
+      <c r="P25" s="39">
         <v>11</v>
       </c>
       <c r="Q25" s="5"/>
       <c r="R25" s="5"/>
     </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:18" x14ac:dyDescent="0.55000000000000004">
       <c r="B26" s="6"/>
       <c r="C26" s="3" t="s">
         <v>27</v>
@@ -2110,7 +2100,7 @@
       <c r="Q26" s="5"/>
       <c r="R26" s="5"/>
     </row>
-    <row r="27" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:18" x14ac:dyDescent="0.55000000000000004">
       <c r="B27" s="6" t="s">
         <v>14</v>
       </c>
@@ -2144,7 +2134,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="2:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:18" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B28" s="6"/>
       <c r="C28" s="3" t="s">
         <v>1</v>
@@ -2182,7 +2172,7 @@
       <c r="O28" s="41"/>
       <c r="P28" s="43"/>
     </row>
-    <row r="29" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:18" x14ac:dyDescent="0.55000000000000004">
       <c r="B29" s="6"/>
       <c r="C29" s="3" t="s">
         <v>19</v>
@@ -2205,7 +2195,7 @@
       <c r="M29" s="5"/>
       <c r="N29" s="5"/>
     </row>
-    <row r="30" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:18" x14ac:dyDescent="0.55000000000000004">
       <c r="B30" s="6"/>
       <c r="C30" s="3" t="s">
         <v>20</v>
@@ -2228,7 +2218,7 @@
       <c r="M30" s="9"/>
       <c r="N30" s="9"/>
     </row>
-    <row r="31" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:18" x14ac:dyDescent="0.55000000000000004">
       <c r="B31" s="6" t="s">
         <v>43</v>
       </c>
@@ -2246,7 +2236,7 @@
       <c r="M31" s="9"/>
       <c r="N31" s="9"/>
     </row>
-    <row r="32" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:18" x14ac:dyDescent="0.55000000000000004">
       <c r="B32" s="6"/>
       <c r="C32" s="3" t="s">
         <v>44</v>
@@ -2270,7 +2260,7 @@
       <c r="M32" s="5"/>
       <c r="N32" s="5"/>
     </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B33" s="6"/>
       <c r="C33" s="3" t="s">
         <v>41</v>
@@ -2294,7 +2284,7 @@
       <c r="M33" s="5"/>
       <c r="N33" s="5"/>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B34" s="6"/>
       <c r="C34" s="3" t="s">
         <v>42</v>
@@ -2318,7 +2308,7 @@
       <c r="M34" s="5"/>
       <c r="N34" s="5"/>
     </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B35" s="6"/>
       <c r="C35" s="3" t="s">
         <v>45</v>
@@ -2337,115 +2327,115 @@
         <v>39</v>
       </c>
     </row>
-    <row r="36" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="D36" s="17"/>
       <c r="E36" s="17"/>
     </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="D37" s="17"/>
       <c r="E37" s="17"/>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="D38" s="17"/>
       <c r="E38" s="17"/>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="D39" s="17"/>
       <c r="E39" s="17"/>
     </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="40" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="D40" s="17"/>
       <c r="E40" s="17"/>
     </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="41" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="D41" s="17"/>
       <c r="E41" s="17"/>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="D42" s="17"/>
       <c r="E42" s="17"/>
     </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="43" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="D43" s="17"/>
       <c r="E43" s="17"/>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="44" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="D44" s="17"/>
       <c r="E44" s="17"/>
     </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="45" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="D45" s="17"/>
       <c r="E45" s="17"/>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="D46" s="17"/>
       <c r="E46" s="17"/>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="D47" s="17"/>
       <c r="E47" s="17"/>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="D48" s="17"/>
       <c r="E48" s="17"/>
     </row>
-    <row r="49" spans="4:5" x14ac:dyDescent="0.4">
+    <row r="49" spans="4:5" x14ac:dyDescent="0.55000000000000004">
       <c r="D49" s="17"/>
       <c r="E49" s="17"/>
     </row>
-    <row r="50" spans="4:5" x14ac:dyDescent="0.4">
+    <row r="50" spans="4:5" x14ac:dyDescent="0.55000000000000004">
       <c r="D50" s="17"/>
       <c r="E50" s="17"/>
     </row>
-    <row r="51" spans="4:5" x14ac:dyDescent="0.4">
+    <row r="51" spans="4:5" x14ac:dyDescent="0.55000000000000004">
       <c r="D51" s="17"/>
       <c r="E51" s="17"/>
     </row>
-    <row r="52" spans="4:5" x14ac:dyDescent="0.4">
+    <row r="52" spans="4:5" x14ac:dyDescent="0.55000000000000004">
       <c r="D52" s="17"/>
       <c r="E52" s="17"/>
     </row>
-    <row r="53" spans="4:5" x14ac:dyDescent="0.4">
+    <row r="53" spans="4:5" x14ac:dyDescent="0.55000000000000004">
       <c r="D53" s="17"/>
       <c r="E53" s="17"/>
     </row>
-    <row r="54" spans="4:5" x14ac:dyDescent="0.4">
+    <row r="54" spans="4:5" x14ac:dyDescent="0.55000000000000004">
       <c r="D54" s="17"/>
       <c r="E54" s="17"/>
     </row>
-    <row r="55" spans="4:5" x14ac:dyDescent="0.4">
+    <row r="55" spans="4:5" x14ac:dyDescent="0.55000000000000004">
       <c r="D55" s="17"/>
       <c r="E55" s="17"/>
     </row>
-    <row r="56" spans="4:5" x14ac:dyDescent="0.4">
+    <row r="56" spans="4:5" x14ac:dyDescent="0.55000000000000004">
       <c r="D56" s="17"/>
       <c r="E56" s="17"/>
     </row>
-    <row r="57" spans="4:5" x14ac:dyDescent="0.4">
+    <row r="57" spans="4:5" x14ac:dyDescent="0.55000000000000004">
       <c r="D57" s="17"/>
       <c r="E57" s="17"/>
     </row>
-    <row r="58" spans="4:5" x14ac:dyDescent="0.4">
+    <row r="58" spans="4:5" x14ac:dyDescent="0.55000000000000004">
       <c r="D58" s="17"/>
       <c r="E58" s="17"/>
     </row>
-    <row r="59" spans="4:5" x14ac:dyDescent="0.4">
+    <row r="59" spans="4:5" x14ac:dyDescent="0.55000000000000004">
       <c r="D59" s="17"/>
       <c r="E59" s="17"/>
     </row>
-    <row r="60" spans="4:5" x14ac:dyDescent="0.4">
+    <row r="60" spans="4:5" x14ac:dyDescent="0.55000000000000004">
       <c r="D60" s="17"/>
       <c r="E60" s="17"/>
     </row>
-    <row r="61" spans="4:5" x14ac:dyDescent="0.4">
+    <row r="61" spans="4:5" x14ac:dyDescent="0.55000000000000004">
       <c r="D61" s="17"/>
       <c r="E61" s="17"/>
     </row>
-    <row r="62" spans="4:5" x14ac:dyDescent="0.4">
+    <row r="62" spans="4:5" x14ac:dyDescent="0.55000000000000004">
       <c r="D62" s="17"/>
       <c r="E62" s="17"/>
     </row>
-    <row r="63" spans="4:5" x14ac:dyDescent="0.4">
+    <row r="63" spans="4:5" x14ac:dyDescent="0.55000000000000004">
       <c r="D63" s="17"/>
       <c r="E63" s="17"/>
     </row>

--- a/コスト表.xlsx
+++ b/コスト表.xlsx
@@ -8,17 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Towa\2026_SpringGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D950500-3C07-4655-B446-118201118A6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86A9F6A8-8934-4D52-BB2D-754BB419AE6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -530,7 +541,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -551,19 +562,6 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -646,21 +644,6 @@
       <right style="thin">
         <color theme="1"/>
       </right>
-      <top style="thin">
-        <color theme="3" tint="0.89999084444715716"/>
-      </top>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
       <top/>
       <bottom style="thin">
         <color theme="1"/>
@@ -668,17 +651,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color theme="1"/>
+      <left style="medium">
+        <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color theme="1"/>
+      <right style="medium">
+        <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color theme="1"/>
+      <top style="medium">
+        <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color theme="1"/>
+      <bottom style="medium">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -686,13 +669,28 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -707,7 +705,7 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -716,13 +714,28 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color indexed="64"/>
       </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -731,58 +744,26 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
+      <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -791,7 +772,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -827,12 +808,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -851,89 +832,80 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -964,6 +936,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1412,7 +1387,7 @@
         <f>COUNTA(H3:H35)</f>
         <v>32</v>
       </c>
-      <c r="L4" s="67"/>
+      <c r="L4" s="64"/>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="7"/>
@@ -1471,7 +1446,7 @@
       </c>
       <c r="L6" s="2">
         <f>SUMIFS(F:F, E:E, "アルファ", H:H, "未完了")</f>
-        <v>11.5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.55000000000000004">
@@ -1519,11 +1494,11 @@
       </c>
       <c r="K8" s="2">
         <f>COUNTIF(H3:H35,J8)</f>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L8" s="2">
         <f>COUNTIF(H:H, "未完了")</f>
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.55000000000000004">
@@ -1549,9 +1524,9 @@
       </c>
       <c r="K9" s="12">
         <f>COUNTIF(H3:H35,J9)</f>
-        <v>7</v>
-      </c>
-      <c r="L9" s="68"/>
+        <v>8</v>
+      </c>
+      <c r="L9" s="65"/>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" s="7" t="s">
@@ -1615,11 +1590,11 @@
       <c r="F12" s="4">
         <v>0.5</v>
       </c>
-      <c r="G12" s="4"/>
-      <c r="H12" s="25" t="s">
+      <c r="G12" s="66"/>
+      <c r="H12" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="I12" s="28"/>
+      <c r="I12" s="27"/>
       <c r="J12" t="s">
         <v>53</v>
       </c>
@@ -1644,12 +1619,12 @@
       <c r="F13" s="4">
         <v>0.5</v>
       </c>
-      <c r="G13" s="27"/>
-      <c r="H13" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="I13" s="28"/>
-      <c r="J13" s="66" t="s">
+      <c r="G13" s="66"/>
+      <c r="H13" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="I13" s="27"/>
+      <c r="J13" s="63" t="s">
         <v>52</v>
       </c>
       <c r="K13" s="5">
@@ -1673,11 +1648,11 @@
       <c r="F14" s="4">
         <v>0.5</v>
       </c>
-      <c r="G14" s="27"/>
-      <c r="H14" s="32" t="s">
+      <c r="G14" s="26"/>
+      <c r="H14" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="I14" s="28"/>
+      <c r="I14" s="27"/>
       <c r="J14" s="10"/>
       <c r="K14" s="5"/>
       <c r="L14" s="5"/>
@@ -1696,12 +1671,12 @@
       <c r="F15" s="4">
         <v>1</v>
       </c>
-      <c r="G15" s="27"/>
-      <c r="H15" s="31" t="s">
+      <c r="G15" s="26"/>
+      <c r="H15" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="I15" s="28"/>
-      <c r="J15" s="44" t="s">
+      <c r="I15" s="27"/>
+      <c r="J15" s="41" t="s">
         <v>54</v>
       </c>
       <c r="M15" s="5"/>
@@ -1725,30 +1700,30 @@
       <c r="F16" s="4">
         <v>1</v>
       </c>
-      <c r="G16" s="27"/>
-      <c r="H16" s="31" t="s">
+      <c r="G16" s="26"/>
+      <c r="H16" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="I16" s="28"/>
-      <c r="J16" s="34" t="s">
+      <c r="I16" s="27"/>
+      <c r="J16" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="K16" s="35" t="s">
+      <c r="K16" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="L16" s="35" t="s">
+      <c r="L16" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="M16" s="35" t="s">
+      <c r="M16" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="N16" s="35" t="s">
+      <c r="N16" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="O16" s="36" t="s">
+      <c r="O16" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="P16" s="37" t="s">
+      <c r="P16" s="34" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1766,12 +1741,12 @@
       <c r="F17" s="4">
         <v>1</v>
       </c>
-      <c r="G17" s="27"/>
-      <c r="H17" s="31" t="s">
+      <c r="G17" s="26"/>
+      <c r="H17" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="I17" s="29"/>
-      <c r="J17" s="38">
+      <c r="I17" s="28"/>
+      <c r="J17" s="35">
         <v>1</v>
       </c>
       <c r="K17" s="12">
@@ -1789,7 +1764,7 @@
       <c r="O17" s="12">
         <v>6</v>
       </c>
-      <c r="P17" s="39">
+      <c r="P17" s="36">
         <v>7</v>
       </c>
     </row>
@@ -1801,12 +1776,12 @@
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
       <c r="F18" s="2"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="31" t="s">
+      <c r="G18" s="25"/>
+      <c r="H18" s="29" t="s">
         <v>39</v>
       </c>
       <c r="I18" s="5"/>
-      <c r="J18" s="38">
+      <c r="J18" s="35">
         <v>8</v>
       </c>
       <c r="K18" s="12">
@@ -1824,7 +1799,7 @@
       <c r="O18" s="12">
         <v>13</v>
       </c>
-      <c r="P18" s="39">
+      <c r="P18" s="36">
         <v>14</v>
       </c>
     </row>
@@ -1847,25 +1822,25 @@
         <v>39</v>
       </c>
       <c r="I19" s="5"/>
-      <c r="J19" s="40">
+      <c r="J19" s="37">
         <v>15</v>
       </c>
       <c r="K19" s="12">
         <v>16</v>
       </c>
-      <c r="L19" s="49">
+      <c r="L19" s="46">
         <v>17</v>
       </c>
-      <c r="M19" s="49">
+      <c r="M19" s="46">
         <v>18</v>
       </c>
-      <c r="N19" s="49">
+      <c r="N19" s="46">
         <v>19</v>
       </c>
-      <c r="O19" s="50">
+      <c r="O19" s="47">
         <v>20</v>
       </c>
-      <c r="P19" s="51">
+      <c r="P19" s="48">
         <v>21</v>
       </c>
     </row>
@@ -1888,25 +1863,25 @@
         <v>39</v>
       </c>
       <c r="I20" s="5"/>
-      <c r="J20" s="52">
+      <c r="J20" s="49">
         <v>22</v>
       </c>
-      <c r="K20" s="49">
+      <c r="K20" s="46">
         <v>23</v>
       </c>
-      <c r="L20" s="49">
+      <c r="L20" s="46">
         <v>24</v>
       </c>
-      <c r="M20" s="49">
+      <c r="M20" s="46">
         <v>25</v>
       </c>
-      <c r="N20" s="49">
+      <c r="N20" s="46">
         <v>26</v>
       </c>
-      <c r="O20" s="50">
+      <c r="O20" s="47">
         <v>27</v>
       </c>
-      <c r="P20" s="51">
+      <c r="P20" s="48">
         <v>28</v>
       </c>
     </row>
@@ -1923,19 +1898,19 @@
         <v>39</v>
       </c>
       <c r="I21" s="5"/>
-      <c r="J21" s="53">
+      <c r="J21" s="50">
         <v>29</v>
       </c>
-      <c r="K21" s="54">
+      <c r="K21" s="51">
         <v>30</v>
       </c>
-      <c r="L21" s="54">
+      <c r="L21" s="51">
         <v>31</v>
       </c>
-      <c r="M21" s="41"/>
-      <c r="N21" s="41"/>
-      <c r="O21" s="42"/>
-      <c r="P21" s="43"/>
+      <c r="M21" s="38"/>
+      <c r="N21" s="38"/>
+      <c r="O21" s="39"/>
+      <c r="P21" s="40"/>
     </row>
     <row r="22" spans="2:18" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B22" s="6"/>
@@ -1976,7 +1951,7 @@
       <c r="H23" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="J23" s="45" t="s">
+      <c r="J23" s="42" t="s">
         <v>62</v>
       </c>
       <c r="Q23" s="5"/>
@@ -1994,19 +1969,19 @@
       <c r="H24" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="J24" s="46"/>
-      <c r="K24" s="48"/>
-      <c r="L24" s="48"/>
-      <c r="M24" s="55">
+      <c r="J24" s="43"/>
+      <c r="K24" s="45"/>
+      <c r="L24" s="45"/>
+      <c r="M24" s="52">
         <v>1</v>
       </c>
-      <c r="N24" s="55">
+      <c r="N24" s="52">
         <v>2</v>
       </c>
-      <c r="O24" s="55">
+      <c r="O24" s="52">
         <v>3</v>
       </c>
-      <c r="P24" s="56">
+      <c r="P24" s="53">
         <v>4</v>
       </c>
       <c r="Q24" s="5"/>
@@ -2032,25 +2007,25 @@
       <c r="H25" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="J25" s="57">
+      <c r="J25" s="54">
         <v>5</v>
       </c>
-      <c r="K25" s="58">
+      <c r="K25" s="55">
         <v>6</v>
       </c>
-      <c r="L25" s="59">
+      <c r="L25" s="56">
         <v>7</v>
       </c>
-      <c r="M25" s="60">
+      <c r="M25" s="57">
         <v>8</v>
       </c>
-      <c r="N25" s="60">
+      <c r="N25" s="57">
         <v>9</v>
       </c>
-      <c r="O25" s="60">
+      <c r="O25" s="57">
         <v>10</v>
       </c>
-      <c r="P25" s="39">
+      <c r="P25" s="36">
         <v>11</v>
       </c>
       <c r="Q25" s="5"/>
@@ -2076,10 +2051,10 @@
       <c r="H26" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="J26" s="38">
+      <c r="J26" s="35">
         <v>12</v>
       </c>
-      <c r="K26" s="61">
+      <c r="K26" s="58">
         <v>13</v>
       </c>
       <c r="L26" s="12">
@@ -2094,7 +2069,7 @@
       <c r="O26" s="12">
         <v>17</v>
       </c>
-      <c r="P26" s="39">
+      <c r="P26" s="36">
         <v>18</v>
       </c>
       <c r="Q26" s="5"/>
@@ -2112,10 +2087,10 @@
       <c r="H27" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="J27" s="38">
+      <c r="J27" s="35">
         <v>19</v>
       </c>
-      <c r="K27" s="33">
+      <c r="K27" s="30">
         <v>20</v>
       </c>
       <c r="L27" s="12">
@@ -2130,7 +2105,7 @@
       <c r="O27" s="12">
         <v>24</v>
       </c>
-      <c r="P27" s="39">
+      <c r="P27" s="36">
         <v>25</v>
       </c>
     </row>
@@ -2154,23 +2129,23 @@
       <c r="H28" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="J28" s="47">
+      <c r="J28" s="44">
         <v>26</v>
       </c>
-      <c r="K28" s="42">
+      <c r="K28" s="39">
         <v>27</v>
       </c>
-      <c r="L28" s="41">
+      <c r="L28" s="38">
         <v>28</v>
       </c>
-      <c r="M28" s="41">
+      <c r="M28" s="38">
         <v>29</v>
       </c>
-      <c r="N28" s="41">
+      <c r="N28" s="38">
         <v>30</v>
       </c>
-      <c r="O28" s="41"/>
-      <c r="P28" s="43"/>
+      <c r="O28" s="38"/>
+      <c r="P28" s="40"/>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.55000000000000004">
       <c r="B29" s="6"/>
@@ -2230,7 +2205,7 @@
       <c r="H31" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="J31" s="62" t="s">
+      <c r="J31" s="59" t="s">
         <v>35</v>
       </c>
       <c r="M31" s="9"/>
@@ -2254,7 +2229,7 @@
       <c r="H32" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="J32" s="63" t="s">
+      <c r="J32" s="60" t="s">
         <v>36</v>
       </c>
       <c r="M32" s="5"/>
@@ -2278,7 +2253,7 @@
       <c r="H33" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="J33" s="64" t="s">
+      <c r="J33" s="61" t="s">
         <v>38</v>
       </c>
       <c r="M33" s="5"/>
@@ -2302,7 +2277,7 @@
       <c r="H34" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="J34" s="65" t="s">
+      <c r="J34" s="62" t="s">
         <v>63</v>
       </c>
       <c r="M34" s="5"/>

--- a/コスト表.xlsx
+++ b/コスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Towa\2026_SpringGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86A9F6A8-8934-4D52-BB2D-754BB419AE6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7944AD58-83B7-4C3C-B01C-B3B44DF9A522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="L5" s="2">
         <f>SUMIFS(F:F, E:E, "プロト", H:H, "未完了")</f>
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.55000000000000004">
@@ -1485,20 +1485,22 @@
       <c r="F8" s="2">
         <v>0.5</v>
       </c>
-      <c r="G8" s="2"/>
+      <c r="G8" s="2">
+        <v>0.5</v>
+      </c>
       <c r="H8" s="18" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="J8" s="24" t="s">
         <v>39</v>
       </c>
       <c r="K8" s="2">
         <f>COUNTIF(H3:H35,J8)</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L8" s="2">
         <f>COUNTIF(H:H, "未完了")</f>
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.55000000000000004">
@@ -1524,7 +1526,7 @@
       </c>
       <c r="K9" s="12">
         <f>COUNTIF(H3:H35,J9)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L9" s="65"/>
     </row>

--- a/コスト表.xlsx
+++ b/コスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Towa\2026_SpringGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7944AD58-83B7-4C3C-B01C-B3B44DF9A522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67CFE9AA-C9BD-452B-B1AF-26194E2FAA8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="K12" s="5">
         <f ca="1">DATE(2026,4,17)-TODAY()</f>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L12" s="9"/>
       <c r="M12" s="9"/>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="K13" s="5">
         <f ca="1">K11/K12</f>
-        <v>0.94</v>
+        <v>0.97916666666666663</v>
       </c>
       <c r="L13" s="5"/>
       <c r="M13" s="5"/>

--- a/コスト表.xlsx
+++ b/コスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Towa\2026_SpringGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67CFE9AA-C9BD-452B-B1AF-26194E2FAA8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AF6576B-3C8B-463D-99C4-CDCD4FF8DF2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="L6" s="2">
         <f>SUMIFS(F:F, E:E, "アルファ", H:H, "未完了")</f>
-        <v>11</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.55000000000000004">
@@ -1496,11 +1496,11 @@
       </c>
       <c r="K8" s="2">
         <f>COUNTIF(H3:H35,J8)</f>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L8" s="2">
         <f>COUNTIF(H:H, "未完了")</f>
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.55000000000000004">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="K9" s="12">
         <f>COUNTIF(H3:H35,J9)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L9" s="65"/>
     </row>
@@ -1564,9 +1564,11 @@
       <c r="F11" s="4">
         <v>0.5</v>
       </c>
-      <c r="G11" s="4"/>
+      <c r="G11" s="4">
+        <v>0.5</v>
+      </c>
       <c r="H11" s="18" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="I11" s="5"/>
       <c r="J11" t="s">
@@ -1602,7 +1604,7 @@
       </c>
       <c r="K12" s="5">
         <f ca="1">DATE(2026,4,17)-TODAY()</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L12" s="9"/>
       <c r="M12" s="9"/>
@@ -1621,7 +1623,9 @@
       <c r="F13" s="4">
         <v>0.5</v>
       </c>
-      <c r="G13" s="66"/>
+      <c r="G13" s="66">
+        <v>0.5</v>
+      </c>
       <c r="H13" s="18" t="s">
         <v>46</v>
       </c>
@@ -1631,7 +1635,7 @@
       </c>
       <c r="K13" s="5">
         <f ca="1">K11/K12</f>
-        <v>0.97916666666666663</v>
+        <v>1.0217391304347827</v>
       </c>
       <c r="L13" s="5"/>
       <c r="M13" s="5"/>

--- a/コスト表.xlsx
+++ b/コスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Towa\2026_SpringGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AF6576B-3C8B-463D-99C4-CDCD4FF8DF2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23D138FC-D5F9-4911-8AAE-1A1BBB5CA9DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="65">
   <si>
     <t>アニメーション</t>
     <phoneticPr fontId="2"/>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K4" s="2">
         <f>COUNTA(H3:H35)</f>
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="L4" s="64"/>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="L5" s="2">
         <f>SUMIFS(F:F, E:E, "プロト", H:H, "未完了")</f>
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.55000000000000004">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="L6" s="2">
         <f>SUMIFS(F:F, E:E, "アルファ", H:H, "未完了")</f>
-        <v>10.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.55000000000000004">
@@ -1496,11 +1496,11 @@
       </c>
       <c r="K8" s="2">
         <f>COUNTIF(H3:H35,J8)</f>
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="L8" s="2">
         <f>COUNTIF(H:H, "未完了")</f>
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.55000000000000004">
@@ -1517,16 +1517,18 @@
       <c r="F9" s="2">
         <v>0.5</v>
       </c>
-      <c r="G9" s="4"/>
+      <c r="G9" s="4">
+        <v>0.5</v>
+      </c>
       <c r="H9" s="18" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="J9" s="23" t="s">
         <v>46</v>
       </c>
       <c r="K9" s="12">
         <f>COUNTIF(H3:H35,J9)</f>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L9" s="65"/>
     </row>
@@ -1539,9 +1541,7 @@
       <c r="E10" s="1"/>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
-      <c r="H10" s="18" t="s">
-        <v>39</v>
-      </c>
+      <c r="H10" s="18"/>
       <c r="I10" s="5"/>
       <c r="J10" s="11"/>
       <c r="K10" s="5"/>
@@ -1677,9 +1677,11 @@
       <c r="F15" s="4">
         <v>1</v>
       </c>
-      <c r="G15" s="26"/>
+      <c r="G15" s="26">
+        <v>1</v>
+      </c>
       <c r="H15" s="29" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="I15" s="27"/>
       <c r="J15" s="41" t="s">
@@ -1706,9 +1708,11 @@
       <c r="F16" s="4">
         <v>1</v>
       </c>
-      <c r="G16" s="26"/>
+      <c r="G16" s="26">
+        <v>0.5</v>
+      </c>
       <c r="H16" s="29" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="I16" s="27"/>
       <c r="J16" s="31" t="s">
@@ -1747,9 +1751,11 @@
       <c r="F17" s="4">
         <v>1</v>
       </c>
-      <c r="G17" s="26"/>
+      <c r="G17" s="26">
+        <v>0.5</v>
+      </c>
       <c r="H17" s="29" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="I17" s="28"/>
       <c r="J17" s="35">
@@ -1783,9 +1789,7 @@
       <c r="E18" s="1"/>
       <c r="F18" s="2"/>
       <c r="G18" s="25"/>
-      <c r="H18" s="29" t="s">
-        <v>39</v>
-      </c>
+      <c r="H18" s="29"/>
       <c r="I18" s="5"/>
       <c r="J18" s="35">
         <v>8</v>
@@ -1900,9 +1904,7 @@
       <c r="E21" s="1"/>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
-      <c r="H21" s="18" t="s">
-        <v>39</v>
-      </c>
+      <c r="H21" s="18"/>
       <c r="I21" s="5"/>
       <c r="J21" s="50">
         <v>29</v>
@@ -2090,9 +2092,7 @@
       <c r="E27" s="1"/>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
-      <c r="H27" s="18" t="s">
-        <v>39</v>
-      </c>
+      <c r="H27" s="18"/>
       <c r="J27" s="35">
         <v>19</v>
       </c>
@@ -2208,9 +2208,7 @@
       <c r="E31" s="1"/>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
-      <c r="H31" s="18" t="s">
-        <v>39</v>
-      </c>
+      <c r="H31" s="18"/>
       <c r="J31" s="59" t="s">
         <v>35</v>
       </c>

--- a/コスト表.xlsx
+++ b/コスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Towa\2026_SpringGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23D138FC-D5F9-4911-8AAE-1A1BBB5CA9DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BBE6CBD-89CF-4303-A8CD-C9FC76AACE22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="L5" s="2">
         <f>SUMIFS(F:F, E:E, "プロト", H:H, "未完了")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.55000000000000004">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="L6" s="2">
         <f>SUMIFS(F:F, E:E, "アルファ", H:H, "未完了")</f>
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.55000000000000004">
@@ -1496,11 +1496,11 @@
       </c>
       <c r="K8" s="2">
         <f>COUNTIF(H3:H35,J8)</f>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L8" s="2">
         <f>COUNTIF(H:H, "未完了")</f>
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.55000000000000004">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K9" s="12">
         <f>COUNTIF(H3:H35,J9)</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L9" s="65"/>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="K12" s="5">
         <f ca="1">DATE(2026,4,17)-TODAY()</f>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L12" s="9"/>
       <c r="M12" s="9"/>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="K13" s="5">
         <f ca="1">K11/K12</f>
-        <v>1.0217391304347827</v>
+        <v>1.0681818181818181</v>
       </c>
       <c r="L13" s="5"/>
       <c r="M13" s="5"/>
@@ -1934,9 +1934,11 @@
       <c r="F22" s="8">
         <v>1</v>
       </c>
-      <c r="G22" s="2"/>
+      <c r="G22" s="2">
+        <v>0.5</v>
+      </c>
       <c r="H22" s="18" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="J22" s="5"/>
       <c r="K22" s="5"/>
@@ -1955,9 +1957,11 @@
       <c r="F23" s="8">
         <v>1</v>
       </c>
-      <c r="G23" s="2"/>
+      <c r="G23" s="2">
+        <v>0.5</v>
+      </c>
       <c r="H23" s="18" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="J23" s="42" t="s">
         <v>62</v>

--- a/コスト表.xlsx
+++ b/コスト表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Towa\2026_SpringGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BBE6CBD-89CF-4303-A8CD-C9FC76AACE22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBE02C87-D16E-41A0-B49C-ACFB0ACEE10E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="L6" s="2">
         <f>SUMIFS(F:F, E:E, "アルファ", H:H, "未完了")</f>
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.55000000000000004">
@@ -1496,11 +1496,11 @@
       </c>
       <c r="K8" s="2">
         <f>COUNTIF(H3:H35,J8)</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L8" s="2">
         <f>COUNTIF(H:H, "未完了")</f>
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.55000000000000004">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K9" s="12">
         <f>COUNTIF(H3:H35,J9)</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L9" s="65"/>
     </row>
@@ -1594,9 +1594,11 @@
       <c r="F12" s="4">
         <v>0.5</v>
       </c>
-      <c r="G12" s="66"/>
+      <c r="G12" s="66">
+        <v>0.5</v>
+      </c>
       <c r="H12" s="18" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="I12" s="27"/>
       <c r="J12" t="s">
@@ -1604,7 +1606,7 @@
       </c>
       <c r="K12" s="5">
         <f ca="1">DATE(2026,4,17)-TODAY()</f>
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="L12" s="9"/>
       <c r="M12" s="9"/>
@@ -1635,7 +1637,7 @@
       </c>
       <c r="K13" s="5">
         <f ca="1">K11/K12</f>
-        <v>1.0681818181818181</v>
+        <v>1.3055555555555556</v>
       </c>
       <c r="L13" s="5"/>
       <c r="M13" s="5"/>
@@ -1654,9 +1656,11 @@
       <c r="F14" s="4">
         <v>0.5</v>
       </c>
-      <c r="G14" s="26"/>
+      <c r="G14" s="26">
+        <v>0.5</v>
+      </c>
       <c r="H14" s="29" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="I14" s="27"/>
       <c r="J14" s="10"/>

--- a/コスト表.xlsx
+++ b/コスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Towa\2026_SpringGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBE02C87-D16E-41A0-B49C-ACFB0ACEE10E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C00D2BB9-51E7-4ACA-9AC6-CC0762E14872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
@@ -1433,9 +1433,11 @@
       <c r="F6" s="8">
         <v>1</v>
       </c>
-      <c r="G6" s="8"/>
+      <c r="G6" s="8">
+        <v>1</v>
+      </c>
       <c r="H6" s="18" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="J6" s="20" t="s">
         <v>36</v>
@@ -1446,7 +1448,7 @@
       </c>
       <c r="L6" s="2">
         <f>SUMIFS(F:F, E:E, "アルファ", H:H, "未完了")</f>
-        <v>5.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.55000000000000004">
@@ -1496,11 +1498,11 @@
       </c>
       <c r="K8" s="2">
         <f>COUNTIF(H3:H35,J8)</f>
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L8" s="2">
         <f>COUNTIF(H:H, "未完了")</f>
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.55000000000000004">
@@ -1528,7 +1530,7 @@
       </c>
       <c r="K9" s="12">
         <f>COUNTIF(H3:H35,J9)</f>
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="L9" s="65"/>
     </row>
@@ -1606,7 +1608,7 @@
       </c>
       <c r="K12" s="5">
         <f ca="1">DATE(2026,4,17)-TODAY()</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L12" s="9"/>
       <c r="M12" s="9"/>
@@ -1637,7 +1639,7 @@
       </c>
       <c r="K13" s="5">
         <f ca="1">K11/K12</f>
-        <v>1.3055555555555556</v>
+        <v>1.46875</v>
       </c>
       <c r="L13" s="5"/>
       <c r="M13" s="5"/>
@@ -1831,9 +1833,11 @@
       <c r="F19" s="8">
         <v>1</v>
       </c>
-      <c r="G19" s="2"/>
+      <c r="G19" s="2">
+        <v>1</v>
+      </c>
       <c r="H19" s="18" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="I19" s="5"/>
       <c r="J19" s="37">
@@ -1872,9 +1876,11 @@
       <c r="F20" s="8">
         <v>1</v>
       </c>
-      <c r="G20" s="2"/>
+      <c r="G20" s="2">
+        <v>1</v>
+      </c>
       <c r="H20" s="18" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="I20" s="5"/>
       <c r="J20" s="49">
@@ -2237,9 +2243,11 @@
       <c r="F32" s="2">
         <v>1</v>
       </c>
-      <c r="G32" s="2"/>
+      <c r="G32" s="2">
+        <v>0.5</v>
+      </c>
       <c r="H32" s="18" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="J32" s="60" t="s">
         <v>36</v>

--- a/コスト表.xlsx
+++ b/コスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Towa\2026_SpringGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C00D2BB9-51E7-4ACA-9AC6-CC0762E14872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{291D03ED-B17F-4662-BECF-4A2934462F79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="64">
   <si>
     <t>アニメーション</t>
     <phoneticPr fontId="2"/>
@@ -269,13 +269,6 @@
     <t>再生</t>
     <rPh sb="0" eb="2">
       <t>サイセイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>停止</t>
-    <rPh sb="0" eb="2">
-      <t>テイシ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -1274,7 +1267,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{039B1606-320D-4390-8B98-CE6030BB2FAA}">
-  <dimension ref="B1:R63"/>
+  <dimension ref="B1:R62"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="25.33203125" bestFit="1" customWidth="1"/>
@@ -1298,7 +1291,7 @@
         <v>30</v>
       </c>
       <c r="C1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="2:16" x14ac:dyDescent="0.55000000000000004">
@@ -1348,16 +1341,16 @@
         <v>0.5</v>
       </c>
       <c r="H3" s="18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J3" s="22" t="s">
         <v>34</v>
       </c>
       <c r="K3" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="L3" s="22" t="s">
         <v>47</v>
-      </c>
-      <c r="L3" s="22" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.55000000000000004">
@@ -1378,14 +1371,14 @@
         <v>0.5</v>
       </c>
       <c r="H4" s="18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K4" s="2">
-        <f>COUNTA(H3:H35)</f>
-        <v>27</v>
+        <f>COUNTA(H3:H34)</f>
+        <v>25</v>
       </c>
       <c r="L4" s="64"/>
     </row>
@@ -1411,7 +1404,7 @@
         <v>35</v>
       </c>
       <c r="K5" s="2">
-        <f>SUMIF(E3:E35,"プロト",F3:F35)</f>
+        <f>SUMIF(E3:E34,"プロト",F3:F34)</f>
         <v>11</v>
       </c>
       <c r="L5" s="2">
@@ -1422,7 +1415,7 @@
     <row r="6" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="7"/>
       <c r="C6" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D6" s="18" t="s">
         <v>32</v>
@@ -1437,18 +1430,18 @@
         <v>1</v>
       </c>
       <c r="H6" s="18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J6" s="20" t="s">
         <v>36</v>
       </c>
       <c r="K6" s="2">
-        <f>SUMIF(E3:E35,"アルファ",F3:F35)</f>
-        <v>11.5</v>
+        <f>SUMIF(E3:E34,"アルファ",F3:F34)</f>
+        <v>11</v>
       </c>
       <c r="L6" s="2">
         <f>SUMIFS(F:F, E:E, "アルファ", H:H, "未完了")</f>
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.55000000000000004">
@@ -1465,12 +1458,12 @@
         <v>38</v>
       </c>
       <c r="K7" s="2">
-        <f>SUMIF(E3:E35,"ベータ",F3:F35)</f>
+        <f>SUMIF(E3:E34,"ベータ",F3:F34)</f>
         <v>1</v>
       </c>
       <c r="L7" s="2">
         <f>SUMIFS(F:F, E:E, "ベータ", H:H, "未完了")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.55000000000000004">
@@ -1491,18 +1484,18 @@
         <v>0.5</v>
       </c>
       <c r="H8" s="18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J8" s="24" t="s">
         <v>39</v>
       </c>
       <c r="K8" s="2">
-        <f>COUNTIF(H3:H35,J8)</f>
-        <v>5</v>
+        <f>COUNTIF(H3:H34,J8)</f>
+        <v>1</v>
       </c>
       <c r="L8" s="2">
         <f>COUNTIF(H:H, "未完了")</f>
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.55000000000000004">
@@ -1523,14 +1516,14 @@
         <v>0.5</v>
       </c>
       <c r="H9" s="18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J9" s="23" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K9" s="12">
-        <f>COUNTIF(H3:H35,J9)</f>
-        <v>22</v>
+        <f>COUNTIF(H3:H34,J9)</f>
+        <v>24</v>
       </c>
       <c r="L9" s="65"/>
     </row>
@@ -1570,15 +1563,15 @@
         <v>0.5</v>
       </c>
       <c r="H11" s="18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I11" s="5"/>
       <c r="J11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K11">
-        <f>SUM(F3:F35)</f>
-        <v>23.5</v>
+        <f>SUM(F3:F34)</f>
+        <v>23</v>
       </c>
       <c r="M11" s="5"/>
     </row>
@@ -1600,11 +1593,11 @@
         <v>0.5</v>
       </c>
       <c r="H12" s="18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I12" s="27"/>
       <c r="J12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K12" s="5">
         <f ca="1">DATE(2026,4,17)-TODAY()</f>
@@ -1631,15 +1624,15 @@
         <v>0.5</v>
       </c>
       <c r="H13" s="18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I13" s="27"/>
       <c r="J13" s="63" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K13" s="5">
         <f ca="1">K11/K12</f>
-        <v>1.46875</v>
+        <v>1.4375</v>
       </c>
       <c r="L13" s="5"/>
       <c r="M13" s="5"/>
@@ -1662,7 +1655,7 @@
         <v>0.5</v>
       </c>
       <c r="H14" s="29" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I14" s="27"/>
       <c r="J14" s="10"/>
@@ -1687,11 +1680,11 @@
         <v>1</v>
       </c>
       <c r="H15" s="29" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I15" s="27"/>
       <c r="J15" s="41" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M15" s="5"/>
       <c r="N15" s="5"/>
@@ -1718,29 +1711,29 @@
         <v>0.5</v>
       </c>
       <c r="H16" s="29" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I16" s="27"/>
       <c r="J16" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="K16" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="K16" s="32" t="s">
+      <c r="L16" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="L16" s="32" t="s">
+      <c r="M16" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="M16" s="32" t="s">
+      <c r="N16" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="N16" s="32" t="s">
+      <c r="O16" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="O16" s="33" t="s">
+      <c r="P16" s="34" t="s">
         <v>60</v>
-      </c>
-      <c r="P16" s="34" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.55000000000000004">
@@ -1761,7 +1754,7 @@
         <v>0.5</v>
       </c>
       <c r="H17" s="29" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I17" s="28"/>
       <c r="J17" s="35">
@@ -1837,7 +1830,7 @@
         <v>1</v>
       </c>
       <c r="H19" s="18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I19" s="5"/>
       <c r="J19" s="37">
@@ -1880,7 +1873,7 @@
         <v>1</v>
       </c>
       <c r="H20" s="18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I20" s="5"/>
       <c r="J20" s="49">
@@ -1948,7 +1941,7 @@
         <v>0.5</v>
       </c>
       <c r="H22" s="18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J22" s="5"/>
       <c r="K22" s="5"/>
@@ -1971,10 +1964,10 @@
         <v>0.5</v>
       </c>
       <c r="H23" s="18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J23" s="42" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q23" s="5"/>
       <c r="R23" s="5"/>
@@ -1988,9 +1981,7 @@
       <c r="E24" s="1"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
-      <c r="H24" s="18" t="s">
-        <v>39</v>
-      </c>
+      <c r="H24" s="18"/>
       <c r="J24" s="43"/>
       <c r="K24" s="45"/>
       <c r="L24" s="45"/>
@@ -2027,7 +2018,7 @@
         <v>0.5</v>
       </c>
       <c r="H25" s="18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J25" s="54">
         <v>5</v>
@@ -2071,7 +2062,7 @@
         <v>0.5</v>
       </c>
       <c r="H26" s="18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J26" s="35">
         <v>12</v>
@@ -2147,7 +2138,7 @@
         <v>2</v>
       </c>
       <c r="H28" s="18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J28" s="44">
         <v>26</v>
@@ -2185,7 +2176,7 @@
         <v>2</v>
       </c>
       <c r="H29" s="18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M29" s="5"/>
       <c r="N29" s="5"/>
@@ -2208,14 +2199,14 @@
         <v>2</v>
       </c>
       <c r="H30" s="18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M30" s="9"/>
       <c r="N30" s="9"/>
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.55000000000000004">
       <c r="B31" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C31" s="3"/>
       <c r="D31" s="1"/>
@@ -2232,7 +2223,7 @@
     <row r="32" spans="2:18" x14ac:dyDescent="0.55000000000000004">
       <c r="B32" s="6"/>
       <c r="C32" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>33</v>
@@ -2247,7 +2238,7 @@
         <v>0.5</v>
       </c>
       <c r="H32" s="18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J32" s="60" t="s">
         <v>36</v>
@@ -2269,9 +2260,11 @@
       <c r="F33" s="2">
         <v>0.5</v>
       </c>
-      <c r="G33" s="2"/>
+      <c r="G33" s="2">
+        <v>0.5</v>
+      </c>
       <c r="H33" s="18" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J33" s="61" t="s">
         <v>38</v>
@@ -2282,45 +2275,30 @@
     <row r="34" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B34" s="6"/>
       <c r="C34" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>33</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F34" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="G34" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="G34" s="2">
+        <v>0.5</v>
+      </c>
       <c r="H34" s="18" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J34" s="62" t="s">
-        <v>63</v>
-      </c>
-      <c r="M34" s="5"/>
-      <c r="N34" s="5"/>
+        <v>62</v>
+      </c>
     </row>
     <row r="35" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B35" s="6"/>
-      <c r="C35" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F35" s="2">
-        <v>1</v>
-      </c>
-      <c r="G35" s="2"/>
-      <c r="H35" s="18" t="s">
-        <v>39</v>
-      </c>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
     </row>
     <row r="36" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="D36" s="17"/>
@@ -2430,17 +2408,13 @@
       <c r="D62" s="17"/>
       <c r="E62" s="17"/>
     </row>
-    <row r="63" spans="4:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="D63" s="17"/>
-      <c r="E63" s="17"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="2"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D63" xr:uid="{D99FF9D9-52C2-47CC-BC93-4ACF23B2DA2A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D62" xr:uid="{D99FF9D9-52C2-47CC-BC93-4ACF23B2DA2A}">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E63" xr:uid="{3F25CF45-EEFF-4838-8184-2DB508A95967}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E62" xr:uid="{3F25CF45-EEFF-4838-8184-2DB508A95967}">
       <formula1>"プロト,アルファ,ベータ,マスタ"</formula1>
     </dataValidation>
   </dataValidations>
